--- a/data_input/maiz_soil_params_rain.xlsx
+++ b/data_input/maiz_soil_params_rain.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\pyaez_github_test_env\input\new soil evaluation\KB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ming-mayhu/Desktop/毕业论文/qtp-pyaez/data_input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FD96147-AEB5-49FA-854A-105300C42D7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACFC9E2-20D2-CE4E-A1B8-507CF116A400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="15" windowWidth="14610" windowHeight="15585" activeTab="6" xr2:uid="{8AAD9566-BB4C-44D2-B3CE-FD7B121B3AA5}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="28800" windowHeight="16340" xr2:uid="{8AAD9566-BB4C-44D2-B3CE-FD7B121B3AA5}"/>
   </bookViews>
   <sheets>
     <sheet name="SQ1" sheetId="1" r:id="rId1"/>
@@ -247,9 +247,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -287,7 +287,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -393,7 +393,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -535,7 +535,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -544,15 +544,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FACB6447-EEBE-4CDF-97EB-75A776AA2E7F}">
   <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -572,7 +572,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -592,7 +592,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -626,7 +626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -649,7 +649,7 @@
         <v>4.16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>2</v>
       </c>
@@ -672,7 +672,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -692,7 +692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -720,16 +720,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1CF382-BD27-4D55-8B33-6E3E46737D1E}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -749,7 +749,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -769,7 +769,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -803,7 +803,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -817,7 +817,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -831,7 +831,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -854,7 +854,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -877,7 +877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -888,7 +888,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -907,16 +907,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC60B64-85DA-4C3E-886C-1B30B1A1B4F3}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -939,7 +939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -962,7 +962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -973,7 +973,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -984,7 +984,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -1011,7 +1011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>36</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1110,9 +1110,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF1C241F-6D3F-42E9-8DF6-C80C18453197}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -1164,7 +1164,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1175,7 +1175,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1194,12 +1194,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{630D2237-30A6-4886-A54B-80E34ED32BA8}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>28</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>30</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1315,9 +1315,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1360E969-6246-4B45-A0C1-A28BCA2343CA}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>35</v>
       </c>
@@ -1397,7 +1397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1427,16 +1427,16 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE727A56-6128-40D3-B114-446A30773FF7}">
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1533,7 +1533,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -1612,15 +1612,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008864D41C708CC54AABC64DB9F8EC5160" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8280e7c680d5d724f4413038ca100d1d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aecedfd1-a701-4d39-be9b-da32a8dfc2a5" xmlns:ns3="6cc8ca2e-56d8-406d-8e41-68c6b727753a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a78283ead66d0e44d8e1b525c3947135" ns2:_="" ns3:_="">
     <xsd:import namespace="aecedfd1-a701-4d39-be9b-da32a8dfc2a5"/>
@@ -1863,15 +1854,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61D9B97E-2726-43EE-9F6F-AB0281F201DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{88016C37-4A20-47C0-B09F-CE1025F19C6C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1888,4 +1880,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61D9B97E-2726-43EE-9F6F-AB0281F201DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>